--- a/interview_forms/021_special_education_teacher_interview_form--interview_forms.xlsx
+++ b/interview_forms/021_special_education_teacher_interview_form--interview_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>infant_and_child_cpr</t>
+          <t>infant_and_child_cpr_-_basic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Infant and Child CPR</t>
+          <t>Infant and Child CPR - Basic</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>infant_and_child_cpr_-_basic</t>
+          <t>infant_and_child_cpr_-_intermediate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Infant and Child CPR - Basic</t>
+          <t>Infant and Child CPR - Intermediate</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>infant_and_child_cpr_-_intermediate</t>
+          <t>infant_and_child_cpr_-_advanced</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Infant and Child CPR - Intermediate</t>
+          <t>Infant and Child CPR - Advanced</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>infant_and_child_cpr_-_advanced</t>
+          <t>national_association_of_social_workers_(nasw)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Infant and Child CPR - Advanced</t>
+          <t>National Association of Social Workers (NASW)</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>national_association_of_social_workers_(nasw)</t>
+          <t>school_administrator</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>National Association of Social Workers (NASW)</t>
+          <t>School Administrator</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>school_administrator</t>
+          <t>teaching_english_as_a_second_language_(esl)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>School Administrator</t>
+          <t>Teaching English as a Second Language (ESL)</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>teaching_english_as_a_second_language_(esl)</t>
+          <t>trauma_informed_care</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Teaching English as a Second Language (ESL)</t>
+          <t>Trauma Informed Care</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>trauma_informed_care</t>
+          <t>trauma_informed_care_-_basic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Trauma Informed Care</t>
+          <t>Trauma Informed Care - Basic</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>trauma_informed_care_-_basic</t>
+          <t>trauma_informed_care_-_intermediate</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Trauma Informed Care - Basic</t>
+          <t>Trauma Informed Care - Intermediate</t>
         </is>
       </c>
     </row>
@@ -1097,29 +1097,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>trauma_informed_care_-_intermediate</t>
+          <t>trauma_informed_care_-_advanced</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Trauma Informed Care - Intermediate</t>
+          <t>Trauma Informed Care - Advanced</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>teaching_certifications_choices</t>
+          <t>work_history_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>trauma_informed_care_-_advanced</t>
+          <t>3_years</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Trauma Informed Care - Advanced</t>
+          <t>3 years</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3_years</t>
+          <t>5_years</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3 years</t>
+          <t>5 years</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5_years</t>
+          <t>10_years</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>10 years</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10_years</t>
+          <t>15_years</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>10 years</t>
+          <t>15 years</t>
         </is>
       </c>
     </row>
@@ -1182,29 +1182,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15_years</t>
+          <t>more_than_15_years</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15 years</t>
+          <t>More than 15 years</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>work_history_choices</t>
+          <t>job_references_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>more_than_15_years</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>More than 15 years</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Unavailable</t>
         </is>
       </c>
     </row>
@@ -1233,27 +1233,10 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>no_preference</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Unavailable</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>job_references_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>no_preference</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>No preference</t>
         </is>
